--- a/FOOD ORDERING APP.xlsx
+++ b/FOOD ORDERING APP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ba5dca7ca716306/Desktop/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1698" documentId="8_{04BF1753-D9EE-43A1-8E25-5B216BD6CE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{693E97E6-6DA2-4F25-9C19-5D890983F86C}"/>
+  <xr:revisionPtr revIDLastSave="1704" documentId="8_{04BF1753-D9EE-43A1-8E25-5B216BD6CE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5448FE0F-F4D6-422A-81BA-D4392F824033}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="4" xr2:uid="{E0AC0575-332B-409E-9E26-D423FE0C8496}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="4" activeTab="6" xr2:uid="{E0AC0575-332B-409E-9E26-D423FE0C8496}"/>
   </bookViews>
   <sheets>
     <sheet name="1.1 SIGN UP" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1842" uniqueCount="1259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1842" uniqueCount="1260">
   <si>
     <t>APPLICATION NAME</t>
   </si>
@@ -1485,9 +1485,6 @@
     <t>FOA_HD_015</t>
   </si>
   <si>
-    <t>HEADER_LOGOUT_FUNCTIONALITY</t>
-  </si>
-  <si>
     <t>VERIFY USER IS LOGGED OUT ON CLICKING LOGOUT</t>
   </si>
   <si>
@@ -2751,9 +2748,6 @@
     <t>SYSTEM SHOULD DISPLAY ADD TO CART BUTTON</t>
   </si>
   <si>
-    <t>PRODUCT DETAIL_ADD_TO_CART_FUNCTIONALITY</t>
-  </si>
-  <si>
     <t>VERIFY THAT USER CAN ADD PRODUCT TO CART FROM DETAIL VIEW</t>
   </si>
   <si>
@@ -4174,24 +4168,15 @@
     <t>REGISTRATION PAGE SHOULD BE LOADED</t>
   </si>
   <si>
-    <t>VERIFY THAT THE USER REGISTRATION FUNCTIONALITY WORKS AS EXPECTED</t>
-  </si>
-  <si>
     <t>1.2 – SOCIAL MEDIA SIGNUP</t>
   </si>
   <si>
-    <t>VERIFY THAT SOCIAL MEDIA SIGNUP FUNCTIONALITY WORKS AS EXPECTED</t>
-  </si>
-  <si>
     <t>2.1 – EMAIL / MOBILE LOGIN</t>
   </si>
   <si>
     <t>USER SHOULD BE REGISTERED</t>
   </si>
   <si>
-    <t>VERIFY THAT EMAIL AND MOBILE LOGIN FUNCTIONALITY WORKS AS EXPECTED</t>
-  </si>
-  <si>
     <t>3.1 – NAVIGATION TO HOME PAGE</t>
   </si>
   <si>
@@ -4202,9 +4187,6 @@
   </si>
   <si>
     <t>3.2 – HEADER SECTION</t>
-  </si>
-  <si>
-    <t>VERIFY THAT THE HEADER SECTION ELEMENTS AND FUNCTIONALITY WORK AS EXPECTED</t>
   </si>
   <si>
     <t>3.2.1.1 – PROFILE MANAGEMENT PAGE</t>
@@ -4234,6 +4216,27 @@
     <t>PIZZA
 BURGER!$
 PASTA123</t>
+  </si>
+  <si>
+    <t>VERIFY THAT THE USER REGISTRATION FUNCTIONALITYITY WORKS AS EXPECTED</t>
+  </si>
+  <si>
+    <t>FUNCTIONALITY TESTING</t>
+  </si>
+  <si>
+    <t>VERIFY THAT SOCIAL MEDIA SIGNUP FUNCTIONALITYITY WORKS AS EXPECTED</t>
+  </si>
+  <si>
+    <t>VERIFY THAT EMAIL AND MOBILE LOGIN FUNCTIONALITYITY WORKS AS EXPECTED</t>
+  </si>
+  <si>
+    <t>VERIFY THAT THE HEADER SECTION ELEMENTS AND FUNCTIONALITYITY WORK AS EXPECTED</t>
+  </si>
+  <si>
+    <t>HEADER_LOGOUT_FUNCTIONALITYITY</t>
+  </si>
+  <si>
+    <t>PRODUCT DETAIL_ADD_TO_CART_FUNCTIONALITYITY</t>
   </si>
 </sst>
 </file>
@@ -4311,7 +4314,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -4376,9 +4379,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4786,7 +4786,7 @@
         <v>15</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -4794,7 +4794,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -4810,7 +4810,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>1239</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -4821,7 +4821,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>8</v>
@@ -4879,7 +4879,7 @@
         <v>22</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>23</v>
@@ -4906,7 +4906,7 @@
         <v>28</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>29</v>
@@ -4932,7 +4932,7 @@
         <v>32</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>33</v>
@@ -4958,7 +4958,7 @@
         <v>34</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>35</v>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D14" s="19"/>
       <c r="E14" s="23"/>
@@ -5000,7 +5000,7 @@
         <v>44</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>46</v>
@@ -5026,7 +5026,7 @@
         <v>48</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D16" s="20" t="s">
         <v>49</v>
@@ -5052,7 +5052,7 @@
         <v>51</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>52</v>
@@ -5078,7 +5078,7 @@
         <v>53</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D18" s="20" t="s">
         <v>54</v>
@@ -5104,7 +5104,7 @@
         <v>56</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D19" s="20" t="s">
         <v>57</v>
@@ -5130,7 +5130,7 @@
         <v>60</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>61</v>
@@ -5156,7 +5156,7 @@
         <v>73</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>72</v>
@@ -5180,7 +5180,7 @@
         <v>74</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D22" s="20" t="s">
         <v>75</v>
@@ -5206,7 +5206,7 @@
         <v>77</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D23" s="20" t="s">
         <v>78</v>
@@ -5232,7 +5232,7 @@
         <v>80</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D24" s="20" t="s">
         <v>81</v>
@@ -5258,7 +5258,7 @@
         <v>83</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D25" s="20" t="s">
         <v>84</v>
@@ -5284,7 +5284,7 @@
         <v>85</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D26" s="20" t="s">
         <v>86</v>
@@ -5310,7 +5310,7 @@
         <v>88</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D27" s="20" t="s">
         <v>89</v>
@@ -5336,7 +5336,7 @@
         <v>91</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D28" s="20" t="s">
         <v>92</v>
@@ -5362,7 +5362,7 @@
         <v>94</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D29" s="20" t="s">
         <v>95</v>
@@ -5388,7 +5388,7 @@
         <v>97</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D30" s="20" t="s">
         <v>98</v>
@@ -5414,7 +5414,7 @@
         <v>101</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D31" s="20" t="s">
         <v>102</v>
@@ -5440,7 +5440,7 @@
         <v>101</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D32" s="20" t="s">
         <v>102</v>
@@ -5466,7 +5466,7 @@
         <v>114</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D33" s="20" t="s">
         <v>115</v>
@@ -5492,7 +5492,7 @@
         <v>118</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D34" s="20" t="s">
         <v>119</v>
@@ -5518,7 +5518,7 @@
         <v>121</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D35" s="20" t="s">
         <v>122</v>
@@ -5544,7 +5544,7 @@
         <v>124</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D36" s="20" t="s">
         <v>125</v>
@@ -5570,7 +5570,7 @@
         <v>127</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D37" s="20" t="s">
         <v>128</v>
@@ -5596,7 +5596,7 @@
         <v>129</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D38" s="20" t="s">
         <v>130</v>
@@ -5622,7 +5622,7 @@
         <v>133</v>
       </c>
       <c r="C39" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D39" s="20" t="s">
         <v>134</v>
@@ -5648,7 +5648,7 @@
         <v>137</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D40" s="20" t="s">
         <v>138</v>
@@ -5674,7 +5674,7 @@
         <v>141</v>
       </c>
       <c r="C41" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D41" s="20" t="s">
         <v>142</v>
@@ -5700,7 +5700,7 @@
         <v>141</v>
       </c>
       <c r="C42" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D42" s="20" t="s">
         <v>142</v>
@@ -5726,7 +5726,7 @@
         <v>151</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D43" s="20" t="s">
         <v>149</v>
@@ -5752,7 +5752,7 @@
         <v>152</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D44" s="20" t="s">
         <v>149</v>
@@ -5778,7 +5778,7 @@
         <v>155</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D45" s="20" t="s">
         <v>157</v>
@@ -5804,7 +5804,7 @@
         <v>159</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D46" s="20" t="s">
         <v>160</v>
@@ -5828,7 +5828,7 @@
         <v>162</v>
       </c>
       <c r="C47" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D47" s="20" t="s">
         <v>163</v>
@@ -5852,7 +5852,7 @@
         <v>167</v>
       </c>
       <c r="C48" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D48" s="20" t="s">
         <v>168</v>
@@ -5878,7 +5878,7 @@
         <v>171</v>
       </c>
       <c r="C49" s="20" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D49" s="20" t="s">
         <v>172</v>
@@ -5904,7 +5904,7 @@
         <v>175</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D50" s="20" t="s">
         <v>176</v>
@@ -5930,7 +5930,7 @@
         <v>179</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D51" s="20" t="s">
         <v>180</v>
@@ -5956,7 +5956,7 @@
         <v>182</v>
       </c>
       <c r="C52" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D52" s="20" t="s">
         <v>183</v>
@@ -5982,7 +5982,7 @@
         <v>186</v>
       </c>
       <c r="C53" s="20" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D53" s="20" t="s">
         <v>187</v>
@@ -6008,7 +6008,7 @@
         <v>190</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D54" s="20" t="s">
         <v>191</v>
@@ -6095,7 +6095,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>1240</v>
+        <v>1237</v>
       </c>
       <c r="E3" s="6"/>
     </row>
@@ -6104,7 +6104,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="E4" s="6"/>
     </row>
@@ -6122,7 +6122,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1241</v>
+        <v>1255</v>
       </c>
       <c r="E6" s="6"/>
     </row>
@@ -6137,7 +6137,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
@@ -6175,7 +6175,7 @@
         <v>206</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>207</v>
@@ -6195,13 +6195,13 @@
         <v>209</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>210</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>211</v>
@@ -6221,13 +6221,13 @@
         <v>213</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>214</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>215</v>
@@ -6247,13 +6247,13 @@
         <v>216</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>217</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>218</v>
@@ -6273,13 +6273,13 @@
         <v>220</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>221</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>222</v>
@@ -6299,13 +6299,13 @@
         <v>223</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>224</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>225</v>
@@ -6325,13 +6325,13 @@
         <v>227</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>228</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>229</v>
@@ -6351,13 +6351,13 @@
         <v>231</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>232</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>233</v>
@@ -6377,13 +6377,13 @@
         <v>235</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>236</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>237</v>
@@ -6403,13 +6403,13 @@
         <v>239</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>240</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>241</v>
@@ -6490,7 +6490,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>1242</v>
+        <v>1238</v>
       </c>
       <c r="E3" s="6"/>
     </row>
@@ -6499,7 +6499,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1243</v>
+        <v>1239</v>
       </c>
       <c r="E4" s="6"/>
     </row>
@@ -6517,7 +6517,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1244</v>
+        <v>1256</v>
       </c>
       <c r="E6" s="6"/>
     </row>
@@ -6532,7 +6532,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
@@ -6570,7 +6570,7 @@
         <v>300</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="F9" s="12" t="s">
         <v>301</v>
@@ -6590,16 +6590,16 @@
         <v>341</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>304</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>305</v>
@@ -6616,13 +6616,13 @@
         <v>342</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>309</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>58</v>
@@ -6642,13 +6642,13 @@
         <v>343</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>311</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>312</v>
@@ -6668,13 +6668,13 @@
         <v>344</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>320</v>
@@ -6694,13 +6694,13 @@
         <v>345</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>323</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>58</v>
@@ -6720,13 +6720,13 @@
         <v>346</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>324</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>325</v>
@@ -6746,16 +6746,16 @@
         <v>347</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>327</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="G16" s="4" t="s">
         <v>328</v>
@@ -6772,13 +6772,13 @@
         <v>348</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>329</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>330</v>
@@ -6798,13 +6798,13 @@
         <v>349</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>332</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>330</v>
@@ -6824,13 +6824,13 @@
         <v>350</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>333</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>334</v>
@@ -6850,13 +6850,13 @@
         <v>351</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>336</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>188</v>
@@ -6876,13 +6876,13 @@
         <v>352</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>338</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>330</v>
@@ -7093,7 +7093,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -7101,7 +7101,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1246</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -7117,7 +7117,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1247</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -7128,7 +7128,7 @@
         <v>42</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>8</v>
@@ -7160,13 +7160,13 @@
         <v>355</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>356</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>357</v>
@@ -7186,13 +7186,13 @@
         <v>360</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>361</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>362</v>
@@ -7212,13 +7212,13 @@
         <v>364</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>365</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>366</v>
@@ -7238,13 +7238,13 @@
         <v>369</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>370</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>371</v>
@@ -7264,13 +7264,13 @@
         <v>374</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>375</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>376</v>
@@ -7296,7 +7296,7 @@
         <v>380</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>381</v>
@@ -7316,13 +7316,13 @@
         <v>383</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>384</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>385</v>
@@ -7400,7 +7400,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>1248</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -7408,7 +7408,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1246</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -7424,7 +7424,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1249</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -7435,7 +7435,7 @@
         <v>42</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>8</v>
@@ -7473,7 +7473,7 @@
         <v>388</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>207</v>
@@ -7490,13 +7490,13 @@
         <v>391</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>392</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>207</v>
@@ -7513,13 +7513,13 @@
         <v>395</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>396</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>432</v>
@@ -7536,13 +7536,13 @@
         <v>399</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>400</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>401</v>
@@ -7559,13 +7559,13 @@
         <v>404</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>405</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>406</v>
@@ -7582,13 +7582,13 @@
         <v>409</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>410</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>411</v>
@@ -7605,13 +7605,13 @@
         <v>414</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>415</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>416</v>
@@ -7628,13 +7628,13 @@
         <v>419</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>420</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>58</v>
@@ -7651,13 +7651,13 @@
         <v>423</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>424</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>425</v>
@@ -7674,13 +7674,13 @@
         <v>428</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>429</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>430</v>
@@ -7703,7 +7703,7 @@
         <v>435</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>366</v>
@@ -7720,13 +7720,13 @@
         <v>438</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>439</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>207</v>
@@ -7743,13 +7743,13 @@
         <v>442</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>443</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>207</v>
@@ -7766,13 +7766,13 @@
         <v>446</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>447</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>207</v>
@@ -7786,39 +7786,39 @@
         <v>449</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>450</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>451</v>
-      </c>
       <c r="E23" s="5" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>207</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="C24" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>455</v>
-      </c>
       <c r="E24" s="5" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>207</v>
@@ -7829,186 +7829,186 @@
     </row>
     <row r="25" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>456</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="C25" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>458</v>
-      </c>
       <c r="E25" s="5" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>381</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="C26" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>462</v>
-      </c>
       <c r="E26" s="5" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>207</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>464</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="C27" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>466</v>
-      </c>
       <c r="E27" s="5" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>366</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>469</v>
-      </c>
       <c r="C28" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>384</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>385</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>471</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>472</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>207</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="C30" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>476</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="D30" s="4" t="s">
+      <c r="E30" s="5" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>1212</v>
-      </c>
-      <c r="F30" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>478</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="C31" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>482</v>
-      </c>
       <c r="E31" s="5" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>207</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>484</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="C32" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="D32" s="4" t="s">
+      <c r="E32" s="5" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="G32" s="4" t="s">
         <v>486</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>1214</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>478</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
@@ -8073,7 +8073,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -8081,7 +8081,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -8089,7 +8089,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1254</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -8105,7 +8105,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1255</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -8116,7 +8116,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>8</v>
@@ -8142,1796 +8142,1796 @@
     </row>
     <row r="9" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>748</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="E9" s="5" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>750</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>1101</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>686</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>752</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="E10" s="5" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>753</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>1101</v>
-      </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>754</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>756</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>757</v>
-      </c>
       <c r="E11" s="5" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>758</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>759</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="E12" s="5" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>760</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>1103</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>766</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>762</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="E13" s="5" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>763</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>1104</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>764</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>767</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>768</v>
-      </c>
       <c r="E14" s="5" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>207</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>770</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>771</v>
-      </c>
       <c r="E15" s="5" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>207</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>773</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="E16" s="5" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>774</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>1107</v>
-      </c>
-      <c r="F16" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>775</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>776</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>777</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>778</v>
-      </c>
       <c r="E17" s="5" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>241</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>780</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="E18" s="5" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>1231</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>781</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>1156</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>1233</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>782</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D19" s="4" t="s">
         <v>783</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="4" t="s">
+      <c r="E19" s="5" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>784</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>1156</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>754</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B20" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>786</v>
       </c>
-      <c r="C20" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>787</v>
-      </c>
       <c r="E20" s="5" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>789</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="4" t="s">
+      <c r="E21" s="5" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>790</v>
       </c>
-      <c r="E21" s="5" t="s">
-        <v>1158</v>
-      </c>
-      <c r="F21" s="4" t="s">
+      <c r="G21" s="4" t="s">
         <v>791</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>793</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D22" s="4" t="s">
+      <c r="E22" s="5" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>794</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>1159</v>
-      </c>
-      <c r="F22" s="4" t="s">
+      <c r="G22" s="4" t="s">
         <v>795</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>796</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>207</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>800</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="E24" s="5" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>801</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>1161</v>
-      </c>
-      <c r="F24" s="4" t="s">
+      <c r="G24" s="4" t="s">
         <v>802</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>803</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>804</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="4" t="s">
+      <c r="E25" s="5" t="s">
+        <v>1160</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>805</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>1162</v>
-      </c>
-      <c r="F25" s="4" t="s">
+      <c r="G25" s="4" t="s">
         <v>806</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>807</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>807</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>808</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>809</v>
-      </c>
       <c r="E26" s="5" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>207</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>811</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="D27" s="4" t="s">
+      <c r="E27" s="5" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>812</v>
       </c>
-      <c r="E27" s="5" t="s">
-        <v>1164</v>
-      </c>
-      <c r="F27" s="4" t="s">
+      <c r="G27" s="4" t="s">
         <v>813</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>814</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>815</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="D28" s="4" t="s">
+      <c r="E28" s="5" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>816</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>1165</v>
-      </c>
-      <c r="F28" s="4" t="s">
+      <c r="G28" s="4" t="s">
         <v>817</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>818</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D29" s="4" t="s">
+        <v>900</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>902</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>1160</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>903</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>904</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B30" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>904</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>905</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>906</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>1166</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>907</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>908</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>908</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>909</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D31" s="4" t="s">
+      <c r="G31" s="4" t="s">
         <v>910</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>1166</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>911</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>912</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B32" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>913</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D32" s="4" t="s">
+      <c r="G32" s="4" t="s">
         <v>914</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>1167</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>915</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>916</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B33" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>917</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D33" s="4" t="s">
+      <c r="G33" s="4" t="s">
         <v>918</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>1168</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>919</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>920</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B34" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>921</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D34" s="4" t="s">
+      <c r="G34" s="4" t="s">
         <v>922</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>1160</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>923</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>924</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>925</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="D35" s="4" t="s">
+      <c r="G35" s="4" t="s">
         <v>926</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>1169</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>927</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>928</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D36" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="G36" s="4" t="s">
         <v>930</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>1160</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>931</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>932</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B37" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>933</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D37" s="4" t="s">
+      <c r="G37" s="4" t="s">
         <v>934</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>1170</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>935</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>936</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B39" s="4" t="s">
+        <v>938</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>1232</v>
+      </c>
+      <c r="G39" s="4" t="s">
         <v>940</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>941</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>1170</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>1234</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>942</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>942</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>943</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>944</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>1170</v>
-      </c>
-      <c r="F40" s="25" t="s">
-        <v>1258</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>944</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>945</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>1170</v>
+      </c>
+      <c r="F41" s="4" t="s">
         <v>946</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D41" s="4" t="s">
+      <c r="G41" s="4" t="s">
         <v>947</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>1172</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>948</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>949</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>950</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="D42" s="4" t="s">
+      <c r="G42" s="4" t="s">
         <v>951</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>1169</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>952</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D43" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="G43" s="4" t="s">
         <v>955</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>1160</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>956</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>957</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>957</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>958</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D44" s="4" t="s">
+      <c r="G44" s="4" t="s">
         <v>959</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>1170</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>960</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>961</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F45" s="4" t="s">
         <v>962</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D45" s="4" t="s">
+      <c r="G45" s="4" t="s">
         <v>963</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>1173</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>964</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>965</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="B46" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>965</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>1233</v>
+      </c>
+      <c r="G46" s="4" t="s">
         <v>966</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>967</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>1170</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>1235</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>1174</v>
+        <v>1172</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="B48" s="4" t="s">
+        <v>970</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>971</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>1173</v>
+      </c>
+      <c r="F48" s="4" t="s">
         <v>972</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D48" s="4" t="s">
+      <c r="G48" s="4" t="s">
         <v>973</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>1175</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>974</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B49" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F49" s="4" t="s">
         <v>976</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="D49" s="4" t="s">
+      <c r="G49" s="4" t="s">
         <v>977</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>1100</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>978</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>979</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="B51" s="4" t="s">
+        <v>981</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>982</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F51" s="4" t="s">
         <v>983</v>
       </c>
-      <c r="C51" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D51" s="4" t="s">
+      <c r="G51" s="4" t="s">
         <v>984</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>1170</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>985</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>986</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="B52" s="4" t="s">
+        <v>985</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>986</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F52" s="4" t="s">
         <v>987</v>
       </c>
-      <c r="C52" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D52" s="4" t="s">
+      <c r="G52" s="4" t="s">
         <v>988</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>1170</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>989</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="B53" s="4" t="s">
+        <v>989</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>1251</v>
+      </c>
+      <c r="G53" s="4" t="s">
         <v>991</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>992</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>1170</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>1257</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>993</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B54" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>993</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G54" s="4" t="s">
         <v>994</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>995</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>1176</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>1256</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="F55" s="4">
         <v>150</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="B56" s="4" t="s">
+        <v>998</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>999</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F56" s="4" t="s">
         <v>1000</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D56" s="4" t="s">
+      <c r="G56" s="4" t="s">
         <v>1001</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>1169</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>1002</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="F57" s="4">
         <v>4.2</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B58" s="4" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>1006</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>1007</v>
       </c>
-      <c r="C58" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D58" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>1008</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>1170</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>1009</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="B59" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F59" s="4" t="s">
         <v>1011</v>
       </c>
-      <c r="C59" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D59" s="4" t="s">
+      <c r="G59" s="4" t="s">
         <v>1012</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>1170</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>1013</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>1014</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="B60" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>1014</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>1015</v>
       </c>
-      <c r="C60" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D60" s="4" t="s">
+      <c r="G60" s="4" t="s">
         <v>1016</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>1170</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>1018</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="B61" s="4" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>1019</v>
       </c>
-      <c r="C61" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="D61" s="4" t="s">
+      <c r="G61" s="4" t="s">
         <v>1020</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>1170</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>1021</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="B62" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>1176</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>1023</v>
       </c>
-      <c r="C62" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D62" s="4" t="s">
+      <c r="G62" s="4" t="s">
         <v>1024</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>1178</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B63" s="4" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>1167</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>1027</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D63" s="4" t="s">
+      <c r="G63" s="4" t="s">
         <v>1028</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>1169</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>1029</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>1030</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>207</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="B65" s="4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F65" s="4" t="s">
         <v>1034</v>
       </c>
-      <c r="C65" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D65" s="4" t="s">
+      <c r="G65" s="4" t="s">
         <v>1035</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>1160</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>1036</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="B66" s="4" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>1037</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="G66" s="4" t="s">
         <v>1038</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>1039</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>1179</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>1040</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="B67" s="4" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="G67" s="4" t="s">
         <v>1041</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>1042</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>1179</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="B68" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>1178</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="G68" s="4" t="s">
         <v>1044</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>1045</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>1180</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="B69" s="4" t="s">
+        <v>1045</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F69" s="4" t="s">
         <v>1047</v>
       </c>
-      <c r="C69" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D69" s="4" t="s">
+      <c r="G69" s="4" t="s">
         <v>1048</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>1181</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>1049</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>1050</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="B70" s="4" t="s">
+        <v>1049</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="G70" s="4" t="s">
         <v>1051</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>1182</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>1053</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="B71" s="4" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="G71" s="4" t="s">
         <v>1054</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>1055</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>1183</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>1056</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="B72" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D72" s="4" t="s">
         <v>819</v>
       </c>
-      <c r="C72" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D72" s="4" t="s">
+      <c r="E72" s="5" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F72" s="4" t="s">
         <v>820</v>
       </c>
-      <c r="E72" s="5" t="s">
-        <v>1184</v>
-      </c>
-      <c r="F72" s="4" t="s">
+      <c r="G72" s="4" t="s">
         <v>821</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>822</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="B73" s="4" t="s">
+        <v>822</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D73" s="4" t="s">
         <v>823</v>
       </c>
-      <c r="C73" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D73" s="4" t="s">
+      <c r="E73" s="5" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="G73" s="4" t="s">
         <v>824</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>1185</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>825</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="B74" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D74" s="4" t="s">
         <v>826</v>
       </c>
-      <c r="C74" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D74" s="4" t="s">
+      <c r="E74" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="G74" s="4" t="s">
         <v>827</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>1186</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="B75" s="4" t="s">
+        <v>828</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>829</v>
       </c>
-      <c r="C75" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D75" s="4" t="s">
+      <c r="E75" s="5" t="s">
+        <v>1185</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="G75" s="4" t="s">
         <v>830</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>1187</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="B76" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>832</v>
       </c>
-      <c r="C76" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D76" s="4" t="s">
+      <c r="E76" s="5" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="G76" s="4" t="s">
         <v>833</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>1188</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="B77" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>835</v>
       </c>
-      <c r="C77" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D77" s="4" t="s">
+      <c r="E77" s="5" t="s">
+        <v>1187</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="G77" s="4" t="s">
         <v>836</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>1189</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>837</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B78" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>838</v>
       </c>
-      <c r="C78" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D78" s="4" t="s">
+      <c r="E78" s="5" t="s">
+        <v>1188</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="G78" s="4" t="s">
         <v>839</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>1190</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>840</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="B79" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D79" s="4" t="s">
         <v>841</v>
       </c>
-      <c r="C79" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D79" s="4" t="s">
+      <c r="E79" s="5" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="G79" s="4" t="s">
         <v>842</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>1191</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>843</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="B80" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D80" s="4" t="s">
         <v>844</v>
       </c>
-      <c r="C80" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D80" s="4" t="s">
+      <c r="E80" s="5" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="G80" s="4" t="s">
         <v>845</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>1192</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>846</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="B81" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D81" s="4" t="s">
         <v>847</v>
       </c>
-      <c r="C81" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D81" s="4" t="s">
+      <c r="E81" s="5" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="G81" s="4" t="s">
         <v>848</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>1192</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="B82" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>850</v>
       </c>
-      <c r="C82" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D82" s="4" t="s">
+      <c r="E82" s="5" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F82" s="4" t="s">
         <v>851</v>
       </c>
-      <c r="E82" s="5" t="s">
-        <v>1192</v>
-      </c>
-      <c r="F82" s="4" t="s">
+      <c r="G82" s="4" t="s">
         <v>852</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>853</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B83" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D83" s="4" t="s">
         <v>854</v>
       </c>
-      <c r="C83" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D83" s="4" t="s">
+      <c r="E83" s="5" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="G83" s="4" t="s">
         <v>855</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>1192</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>856</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="B84" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>857</v>
       </c>
-      <c r="C84" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D84" s="4" t="s">
+      <c r="E84" s="5" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="G84" s="4" t="s">
         <v>858</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>1192</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="B85" s="4" t="s">
+        <v>1259</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="E85" s="5" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>860</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>861</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>1193</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>821</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>862</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>207</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
@@ -10002,7 +10002,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>1250</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -10010,7 +10010,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -10026,7 +10026,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1252</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -10037,7 +10037,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>8</v>
@@ -10063,10 +10063,10 @@
     </row>
     <row r="9" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>19</v>
@@ -10075,99 +10075,99 @@
         <v>23</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>25</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="150" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="F10" s="20" t="s">
         <v>30</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>509</v>
-      </c>
       <c r="E11" s="8" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>511</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>512</v>
-      </c>
       <c r="E12" s="8" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>37</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>515</v>
-      </c>
       <c r="E13" s="8" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>58</v>
@@ -10178,45 +10178,45 @@
     </row>
     <row r="14" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>49</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>305</v>
@@ -10224,19 +10224,19 @@
     </row>
     <row r="16" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>58</v>
@@ -10247,111 +10247,111 @@
     </row>
     <row r="17" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>61</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>523</v>
-      </c>
       <c r="E18" s="8" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="F18" s="4">
         <v>9876543909</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>78</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>81</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>84</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>58</v>
@@ -10362,19 +10362,19 @@
     </row>
     <row r="22" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>531</v>
-      </c>
       <c r="E22" s="8" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="F22" s="4">
         <v>9876543210</v>
@@ -10385,68 +10385,68 @@
     </row>
     <row r="23" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="D23" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>533</v>
-      </c>
       <c r="E23" s="8" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="F23" s="4">
         <v>123456</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>535</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>536</v>
-      </c>
       <c r="E24" s="8" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="F24" s="4">
         <v>654321</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>95</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>96</v>
@@ -10454,22 +10454,22 @@
     </row>
     <row r="26" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D26" s="4" t="s">
+      <c r="E26" s="8" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>539</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>1119</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>540</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>100</v>
@@ -10477,19 +10477,19 @@
     </row>
     <row r="27" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>45</v>
+        <v>1254</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>58</v>
@@ -10500,505 +10500,505 @@
     </row>
     <row r="28" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D28" s="4" t="s">
+      <c r="E28" s="8" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>543</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>1121</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>490</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>545</v>
       </c>
-      <c r="C29" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>546</v>
-      </c>
       <c r="E29" s="8" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="F29" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>491</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B30" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="4" t="s">
+      <c r="E30" s="8" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>548</v>
       </c>
-      <c r="E30" s="8" t="s">
-        <v>1123</v>
-      </c>
-      <c r="F30" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>549</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>551</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D31" s="4" t="s">
+      <c r="E31" s="8" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>552</v>
       </c>
-      <c r="E31" s="8" t="s">
-        <v>1123</v>
-      </c>
-      <c r="F31" s="4" t="s">
+      <c r="G31" s="4" t="s">
         <v>553</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B32" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>555</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D32" s="4" t="s">
+      <c r="E32" s="8" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="G32" s="4" t="s">
         <v>556</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>1124</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>674</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B33" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D33" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D33" s="4" t="s">
+      <c r="E33" s="8" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>559</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>1125</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>676</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B34" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D34" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D34" s="4" t="s">
+      <c r="E34" s="8" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>562</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>1126</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>675</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D35" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D35" s="4" t="s">
+      <c r="E35" s="8" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>565</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>1127</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>677</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="C36" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D36" s="4" t="s">
+      <c r="E36" s="8" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="G36" s="4" t="s">
         <v>568</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>1127</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>678</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B37" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="D37" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="D37" s="4" t="s">
+      <c r="E37" s="8" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="E37" s="8" t="s">
-        <v>1127</v>
-      </c>
-      <c r="F37" s="4" t="s">
+      <c r="G37" s="4" t="s">
         <v>572</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>575</v>
-      </c>
       <c r="E38" s="8" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="F38" s="4">
         <v>9876543210</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B39" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D39" s="4" t="s">
         <v>577</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D39" s="4" t="s">
+      <c r="E39" s="8" t="s">
+        <v>1111</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="G39" s="4" t="s">
         <v>578</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>679</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D40" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="C40" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>581</v>
-      </c>
       <c r="E40" s="8" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D41" s="4" t="s">
         <v>583</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D41" s="4" t="s">
+      <c r="E41" s="8" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="G41" s="4" t="s">
         <v>584</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>1129</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>494</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D42" s="4" t="s">
+      <c r="E42" s="8" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>587</v>
       </c>
-      <c r="E42" s="8" t="s">
-        <v>1130</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>588</v>
-      </c>
       <c r="G42" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>589</v>
       </c>
-      <c r="C43" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="D43" s="4" t="s">
+      <c r="E43" s="8" t="s">
+        <v>1129</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="E43" s="8" t="s">
-        <v>1131</v>
-      </c>
-      <c r="F43" s="4" t="s">
+      <c r="G43" s="4" t="s">
         <v>591</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>592</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>593</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>748</v>
-      </c>
-      <c r="D44" s="4" t="s">
+      <c r="E44" s="8" t="s">
+        <v>1130</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>594</v>
       </c>
-      <c r="E44" s="8" t="s">
-        <v>1132</v>
-      </c>
-      <c r="F44" s="4" t="s">
+      <c r="G44" s="4" t="s">
         <v>595</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>596</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>597</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D45" s="4" t="s">
+      <c r="E45" s="8" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F45" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="E45" s="8" t="s">
-        <v>1133</v>
-      </c>
-      <c r="F45" s="4" t="s">
+      <c r="G45" s="4" t="s">
         <v>599</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B46" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>601</v>
       </c>
-      <c r="C46" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D46" s="4" t="s">
+      <c r="E46" s="8" t="s">
+        <v>1132</v>
+      </c>
+      <c r="F46" s="4" t="s">
         <v>602</v>
       </c>
-      <c r="E46" s="8" t="s">
-        <v>1134</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>603</v>
-      </c>
       <c r="G46" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>604</v>
       </c>
-      <c r="C47" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D47" s="4" t="s">
+      <c r="E47" s="8" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F47" s="4" t="s">
         <v>605</v>
       </c>
-      <c r="E47" s="8" t="s">
-        <v>1135</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>606</v>
-      </c>
       <c r="G47" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B48" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>608</v>
-      </c>
       <c r="E48" s="8" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>177</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B49" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>611</v>
-      </c>
       <c r="E49" s="8" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>181</v>
@@ -11006,134 +11006,134 @@
     </row>
     <row r="50" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B50" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="C50" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>613</v>
-      </c>
       <c r="E50" s="8" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>188</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B51" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="C51" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>615</v>
-      </c>
       <c r="E51" s="8" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>177</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B52" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>617</v>
       </c>
-      <c r="C52" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D52" s="4" t="s">
+      <c r="E52" s="8" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="G52" s="4" t="s">
         <v>618</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>1140</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>681</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B53" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="C53" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D53" s="4" t="s">
+      <c r="E53" s="8" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="G53" s="4" t="s">
         <v>621</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>1141</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>498</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B54" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>623</v>
       </c>
-      <c r="C54" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>624</v>
-      </c>
       <c r="E54" s="8" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="F54" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="G54" s="4" t="s">
         <v>499</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B55" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>625</v>
       </c>
-      <c r="C55" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>626</v>
-      </c>
       <c r="E55" s="8" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>58</v>
@@ -11144,134 +11144,134 @@
     </row>
     <row r="56" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B56" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>627</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>628</v>
-      </c>
       <c r="E56" s="8" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B57" s="4" t="s">
+        <v>628</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="C57" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D57" s="4" t="s">
+      <c r="E57" s="8" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="G57" s="4" t="s">
         <v>630</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>1143</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>682</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B58" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="C58" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D58" s="4" t="s">
+      <c r="E58" s="8" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>633</v>
       </c>
-      <c r="E58" s="8" t="s">
-        <v>1144</v>
-      </c>
-      <c r="F58" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>634</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B59" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>636</v>
       </c>
-      <c r="C59" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D59" s="4" t="s">
+      <c r="E59" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="G59" s="4" t="s">
         <v>637</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>1145</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>683</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B60" s="4" t="s">
+        <v>638</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>639</v>
       </c>
-      <c r="C60" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D60" s="4" t="s">
+      <c r="E60" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="G60" s="4" t="s">
         <v>640</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>1145</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>684</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>641</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="B61" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="C61" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>643</v>
-      </c>
       <c r="E61" s="8" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>58</v>
@@ -11282,22 +11282,22 @@
     </row>
     <row r="62" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B62" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="C62" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D62" s="4" t="s">
+      <c r="E62" s="8" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>645</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>1147</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>646</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>154</v>
@@ -11305,42 +11305,42 @@
     </row>
     <row r="63" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="B63" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>647</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D63" s="4" t="s">
+      <c r="E63" s="8" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="E63" s="8" t="s">
-        <v>1148</v>
-      </c>
-      <c r="F63" s="4" t="s">
+      <c r="G63" s="4" t="s">
         <v>649</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B64" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>651</v>
       </c>
-      <c r="C64" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>652</v>
-      </c>
       <c r="E64" s="8" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>58</v>
@@ -11351,91 +11351,91 @@
     </row>
     <row r="65" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="B65" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D65" s="4" t="s">
         <v>653</v>
       </c>
-      <c r="C65" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D65" s="4" t="s">
+      <c r="E65" s="8" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="G65" s="4" t="s">
         <v>654</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>1149</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>685</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>655</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="B66" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>656</v>
       </c>
-      <c r="C66" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>657</v>
-      </c>
       <c r="E66" s="8" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>177</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="B67" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="C67" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>659</v>
-      </c>
       <c r="E67" s="8" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>177</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="B68" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>661</v>
       </c>
-      <c r="C68" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>662</v>
-      </c>
       <c r="E68" s="8" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G68" s="4" t="s">
         <v>181</v>
@@ -11443,25 +11443,25 @@
     </row>
     <row r="69" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B69" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>1254</v>
+      </c>
+      <c r="D69" s="4" t="s">
         <v>663</v>
       </c>
-      <c r="C69" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>664</v>
-      </c>
       <c r="E69" s="8" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>177</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">

--- a/FOOD ORDERING APP.xlsx
+++ b/FOOD ORDERING APP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7ba5dca7ca716306/Desktop/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1704" documentId="8_{04BF1753-D9EE-43A1-8E25-5B216BD6CE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5448FE0F-F4D6-422A-81BA-D4392F824033}"/>
+  <xr:revisionPtr revIDLastSave="1708" documentId="8_{04BF1753-D9EE-43A1-8E25-5B216BD6CE58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{140F904E-53D2-4E6E-AC37-F572AA398D64}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="4" activeTab="6" xr2:uid="{E0AC0575-332B-409E-9E26-D423FE0C8496}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E0AC0575-332B-409E-9E26-D423FE0C8496}"/>
   </bookViews>
   <sheets>
     <sheet name="1.1 SIGN UP" sheetId="1" r:id="rId1"/>
@@ -489,9 +489,6 @@
     <t>VERIFY PASSWORD STRENGTH METER SHOWS WEAK</t>
   </si>
   <si>
-    <t>pass123</t>
-  </si>
-  <si>
     <t>SYSTEM SHOULD SHOW PASSWORD STRENGTH AS WEAK AND NOT ALLOW SUBMISSION</t>
   </si>
   <si>
@@ -499,9 +496,6 @@
   </si>
   <si>
     <t>VERIFY PASSWORD STRENGTH METER SHOWS MEDIUM</t>
-  </si>
-  <si>
-    <t>Pass1234</t>
   </si>
   <si>
     <t>SYSTEM SHOULD SHOW PASSWORD STRENGTH AS MEDIUM AND NOT ALLOW SUBMISSION</t>
@@ -4237,6 +4231,12 @@
   </si>
   <si>
     <t>PRODUCT DETAIL_ADD_TO_CART_FUNCTIONALITYITY</t>
+  </si>
+  <si>
+    <t>#Pass123</t>
+  </si>
+  <si>
+    <t>Adad!231</t>
   </si>
 </sst>
 </file>
@@ -4786,7 +4786,7 @@
         <v>15</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -4794,7 +4794,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -4810,7 +4810,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -4821,7 +4821,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D8" s="17" t="s">
         <v>8</v>
@@ -4847,7 +4847,7 @@
     </row>
     <row r="9" spans="1:11" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B9" s="19" t="s">
         <v>18</v>
@@ -4873,13 +4873,13 @@
     </row>
     <row r="10" spans="1:11" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B10" s="19" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D10" s="19" t="s">
         <v>23</v>
@@ -4900,13 +4900,13 @@
     </row>
     <row r="11" spans="1:11" ht="150" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B11" s="19" t="s">
         <v>28</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D11" s="19" t="s">
         <v>29</v>
@@ -4926,13 +4926,13 @@
     </row>
     <row r="12" spans="1:11" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B12" s="19" t="s">
         <v>32</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D12" s="20" t="s">
         <v>33</v>
@@ -4952,13 +4952,13 @@
     </row>
     <row r="13" spans="1:11" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B13" s="19" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>35</v>
@@ -4978,11 +4978,11 @@
     </row>
     <row r="14" spans="1:11" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D14" s="19"/>
       <c r="E14" s="23"/>
@@ -4994,13 +4994,13 @@
     </row>
     <row r="15" spans="1:11" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B15" s="20" t="s">
         <v>44</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>46</v>
@@ -5020,13 +5020,13 @@
     </row>
     <row r="16" spans="1:11" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B16" s="20" t="s">
         <v>48</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D16" s="20" t="s">
         <v>49</v>
@@ -5046,13 +5046,13 @@
     </row>
     <row r="17" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B17" s="20" t="s">
         <v>51</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>52</v>
@@ -5072,13 +5072,13 @@
     </row>
     <row r="18" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B18" s="20" t="s">
         <v>53</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D18" s="20" t="s">
         <v>54</v>
@@ -5098,13 +5098,13 @@
     </row>
     <row r="19" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B19" s="20" t="s">
         <v>56</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D19" s="20" t="s">
         <v>57</v>
@@ -5124,13 +5124,13 @@
     </row>
     <row r="20" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B20" s="20" t="s">
         <v>60</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D20" s="20" t="s">
         <v>61</v>
@@ -5150,13 +5150,13 @@
     </row>
     <row r="21" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B21" s="19" t="s">
         <v>73</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>72</v>
@@ -5174,13 +5174,13 @@
     </row>
     <row r="22" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B22" s="20" t="s">
         <v>74</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D22" s="20" t="s">
         <v>75</v>
@@ -5200,13 +5200,13 @@
     </row>
     <row r="23" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B23" s="20" t="s">
         <v>77</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D23" s="20" t="s">
         <v>78</v>
@@ -5226,13 +5226,13 @@
     </row>
     <row r="24" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B24" s="20" t="s">
         <v>80</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D24" s="20" t="s">
         <v>81</v>
@@ -5252,13 +5252,13 @@
     </row>
     <row r="25" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B25" s="20" t="s">
         <v>83</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D25" s="20" t="s">
         <v>84</v>
@@ -5278,13 +5278,13 @@
     </row>
     <row r="26" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B26" s="20" t="s">
         <v>85</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D26" s="20" t="s">
         <v>86</v>
@@ -5304,13 +5304,13 @@
     </row>
     <row r="27" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B27" s="20" t="s">
         <v>88</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D27" s="20" t="s">
         <v>89</v>
@@ -5330,13 +5330,13 @@
     </row>
     <row r="28" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B28" s="20" t="s">
         <v>91</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D28" s="20" t="s">
         <v>92</v>
@@ -5356,13 +5356,13 @@
     </row>
     <row r="29" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B29" s="20" t="s">
         <v>94</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D29" s="20" t="s">
         <v>95</v>
@@ -5382,13 +5382,13 @@
     </row>
     <row r="30" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B30" s="20" t="s">
         <v>97</v>
       </c>
       <c r="C30" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D30" s="20" t="s">
         <v>98</v>
@@ -5408,13 +5408,13 @@
     </row>
     <row r="31" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B31" s="20" t="s">
         <v>101</v>
       </c>
       <c r="C31" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D31" s="20" t="s">
         <v>102</v>
@@ -5434,13 +5434,13 @@
     </row>
     <row r="32" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B32" s="20" t="s">
         <v>101</v>
       </c>
       <c r="C32" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D32" s="20" t="s">
         <v>102</v>
@@ -5460,13 +5460,13 @@
     </row>
     <row r="33" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B33" s="20" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D33" s="20" t="s">
         <v>115</v>
@@ -5486,13 +5486,13 @@
     </row>
     <row r="34" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B34" s="20" t="s">
         <v>118</v>
       </c>
       <c r="C34" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D34" s="20" t="s">
         <v>119</v>
@@ -5501,7 +5501,7 @@
         <v>113</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G34" s="20" t="s">
         <v>120</v>
@@ -5512,13 +5512,13 @@
     </row>
     <row r="35" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B35" s="20" t="s">
         <v>121</v>
       </c>
       <c r="C35" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D35" s="20" t="s">
         <v>122</v>
@@ -5527,7 +5527,7 @@
         <v>113</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G35" s="20" t="s">
         <v>123</v>
@@ -5538,13 +5538,13 @@
     </row>
     <row r="36" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="19" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B36" s="20" t="s">
         <v>124</v>
       </c>
       <c r="C36" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D36" s="20" t="s">
         <v>125</v>
@@ -5553,7 +5553,7 @@
         <v>113</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G36" s="20" t="s">
         <v>126</v>
@@ -5564,13 +5564,13 @@
     </row>
     <row r="37" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="19" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B37" s="20" t="s">
         <v>127</v>
       </c>
       <c r="C37" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D37" s="20" t="s">
         <v>128</v>
@@ -5590,13 +5590,13 @@
     </row>
     <row r="38" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B38" s="20" t="s">
         <v>129</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D38" s="20" t="s">
         <v>130</v>
@@ -5605,10 +5605,10 @@
         <v>113</v>
       </c>
       <c r="F38" s="20" t="s">
+        <v>1258</v>
+      </c>
+      <c r="G38" s="20" t="s">
         <v>131</v>
-      </c>
-      <c r="G38" s="20" t="s">
-        <v>132</v>
       </c>
       <c r="H38" s="19"/>
       <c r="I38" s="19"/>
@@ -5616,25 +5616,25 @@
     </row>
     <row r="39" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B39" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D39" s="20" t="s">
         <v>133</v>
-      </c>
-      <c r="C39" s="20" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D39" s="20" t="s">
-        <v>134</v>
       </c>
       <c r="E39" s="21" t="s">
         <v>113</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>135</v>
+        <v>1259</v>
       </c>
       <c r="G39" s="20" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="H39" s="19"/>
       <c r="I39" s="19"/>
@@ -5642,25 +5642,25 @@
     </row>
     <row r="40" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C40" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D40" s="20" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E40" s="21" t="s">
         <v>113</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G40" s="20" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H40" s="19"/>
       <c r="I40" s="19"/>
@@ -5668,25 +5668,25 @@
     </row>
     <row r="41" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B41" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="C41" s="20" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="E41" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="F41" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="C41" s="20" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D41" s="20" t="s">
+      <c r="G41" s="20" t="s">
         <v>142</v>
-      </c>
-      <c r="E41" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="F41" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="G41" s="20" t="s">
-        <v>144</v>
       </c>
       <c r="H41" s="19"/>
       <c r="I41" s="19"/>
@@ -5694,25 +5694,25 @@
     </row>
     <row r="42" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="B42" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D42" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="E42" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="F42" s="20" t="s">
         <v>141</v>
       </c>
-      <c r="C42" s="20" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D42" s="20" t="s">
+      <c r="G42" s="20" t="s">
         <v>142</v>
-      </c>
-      <c r="E42" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="F42" s="20" t="s">
-        <v>143</v>
-      </c>
-      <c r="G42" s="20" t="s">
-        <v>144</v>
       </c>
       <c r="H42" s="19"/>
       <c r="I42" s="19"/>
@@ -5720,16 +5720,16 @@
     </row>
     <row r="43" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D43" s="20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E43" s="21" t="s">
         <v>113</v>
@@ -5738,7 +5738,7 @@
         <v>116</v>
       </c>
       <c r="G43" s="20" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="H43" s="19"/>
       <c r="I43" s="19"/>
@@ -5746,25 +5746,25 @@
     </row>
     <row r="44" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="19" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D44" s="20" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E44" s="21" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F44" s="20" t="s">
         <v>116</v>
       </c>
       <c r="G44" s="20" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H44" s="19"/>
       <c r="I44" s="19"/>
@@ -5772,25 +5772,25 @@
     </row>
     <row r="45" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="19" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B45" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D45" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="C45" s="20" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D45" s="20" t="s">
-        <v>157</v>
-      </c>
       <c r="E45" s="21" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F45" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="G45" s="20" t="s">
         <v>156</v>
-      </c>
-      <c r="G45" s="20" t="s">
-        <v>158</v>
       </c>
       <c r="H45" s="19"/>
       <c r="I45" s="19"/>
@@ -5798,23 +5798,23 @@
     </row>
     <row r="46" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="19" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B46" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="E46" s="21" t="s">
         <v>159</v>
-      </c>
-      <c r="C46" s="20" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D46" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="E46" s="21" t="s">
-        <v>161</v>
       </c>
       <c r="F46" s="20"/>
       <c r="G46" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H46" s="19"/>
       <c r="I46" s="19"/>
@@ -5822,23 +5822,23 @@
     </row>
     <row r="47" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="19" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B47" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D47" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="E47" s="21" t="s">
         <v>162</v>
-      </c>
-      <c r="C47" s="20" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D47" s="20" t="s">
-        <v>163</v>
-      </c>
-      <c r="E47" s="21" t="s">
-        <v>164</v>
       </c>
       <c r="F47" s="20"/>
       <c r="G47" s="20" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="H47" s="19"/>
       <c r="I47" s="19"/>
@@ -5846,25 +5846,25 @@
     </row>
     <row r="48" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="19" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B48" s="20" t="s">
+        <v>165</v>
+      </c>
+      <c r="C48" s="20" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D48" s="20" t="s">
+        <v>166</v>
+      </c>
+      <c r="E48" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="F48" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="C48" s="20" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D48" s="20" t="s">
+      <c r="G48" s="20" t="s">
         <v>168</v>
-      </c>
-      <c r="E48" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="F48" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="G48" s="20" t="s">
-        <v>170</v>
       </c>
       <c r="H48" s="19"/>
       <c r="I48" s="19"/>
@@ -5872,25 +5872,25 @@
     </row>
     <row r="49" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="19" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B49" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="C49" s="20" t="s">
+        <v>745</v>
+      </c>
+      <c r="D49" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="E49" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="F49" s="20" t="s">
         <v>171</v>
       </c>
-      <c r="C49" s="20" t="s">
-        <v>747</v>
-      </c>
-      <c r="D49" s="20" t="s">
+      <c r="G49" s="20" t="s">
         <v>172</v>
-      </c>
-      <c r="E49" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="F49" s="20" t="s">
-        <v>173</v>
-      </c>
-      <c r="G49" s="20" t="s">
-        <v>174</v>
       </c>
       <c r="H49" s="19"/>
       <c r="I49" s="19"/>
@@ -5898,25 +5898,25 @@
     </row>
     <row r="50" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C50" s="20" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D50" s="20" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F50" s="20">
         <v>123456</v>
       </c>
       <c r="G50" s="20" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H50" s="19"/>
       <c r="I50" s="19"/>
@@ -5924,25 +5924,25 @@
     </row>
     <row r="51" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="19" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C51" s="20" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D51" s="20" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E51" s="21" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F51" s="20" t="s">
         <v>112</v>
       </c>
       <c r="G51" s="20" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H51" s="19"/>
       <c r="I51" s="19"/>
@@ -5950,25 +5950,25 @@
     </row>
     <row r="52" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="19" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B52" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="C52" s="20" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D52" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="E52" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="F52" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="C52" s="20" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D52" s="20" t="s">
+      <c r="G52" s="20" t="s">
         <v>183</v>
-      </c>
-      <c r="E52" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="F52" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="G52" s="20" t="s">
-        <v>185</v>
       </c>
       <c r="H52" s="19"/>
       <c r="I52" s="19"/>
@@ -5976,25 +5976,25 @@
     </row>
     <row r="53" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="19" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B53" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="C53" s="20" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D53" s="20" t="s">
+        <v>185</v>
+      </c>
+      <c r="E53" s="21" t="s">
+        <v>196</v>
+      </c>
+      <c r="F53" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="C53" s="20" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D53" s="20" t="s">
+      <c r="G53" s="20" t="s">
         <v>187</v>
-      </c>
-      <c r="E53" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="F53" s="20" t="s">
-        <v>188</v>
-      </c>
-      <c r="G53" s="20" t="s">
-        <v>189</v>
       </c>
       <c r="H53" s="19"/>
       <c r="I53" s="19"/>
@@ -6002,25 +6002,25 @@
     </row>
     <row r="54" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="19" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B54" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="C54" s="20" t="s">
+        <v>745</v>
+      </c>
+      <c r="D54" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="E54" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="F54" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="G54" s="20" t="s">
         <v>190</v>
-      </c>
-      <c r="C54" s="20" t="s">
-        <v>747</v>
-      </c>
-      <c r="D54" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="E54" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="F54" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="G54" s="20" t="s">
-        <v>192</v>
       </c>
       <c r="H54" s="19"/>
       <c r="I54" s="19"/>
@@ -6028,7 +6028,7 @@
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="24" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B56" s="21" t="s">
         <v>24</v>
@@ -6036,17 +6036,17 @@
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="24" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="24" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -6095,7 +6095,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="E3" s="6"/>
     </row>
@@ -6104,7 +6104,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="E4" s="6"/>
     </row>
@@ -6122,7 +6122,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="E6" s="6"/>
     </row>
@@ -6137,7 +6137,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
@@ -6163,25 +6163,25 @@
     </row>
     <row r="9" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>1219</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>206</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>1221</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>208</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
@@ -6189,25 +6189,25 @@
     </row>
     <row r="10" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>1220</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>210</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>1222</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>212</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
@@ -6215,25 +6215,25 @@
     </row>
     <row r="11" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>1223</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>215</v>
-      </c>
       <c r="G11" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
@@ -6241,25 +6241,25 @@
     </row>
     <row r="12" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>217</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>1224</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>218</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>219</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="13" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>220</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>1225</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>222</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>103</v>
@@ -6293,25 +6293,25 @@
     </row>
     <row r="14" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>1224</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>224</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>1226</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>226</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -6319,25 +6319,25 @@
     </row>
     <row r="15" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>1225</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>228</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>1227</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>230</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
@@ -6345,25 +6345,25 @@
     </row>
     <row r="16" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>1226</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>232</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>1228</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>234</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
@@ -6371,25 +6371,25 @@
     </row>
     <row r="17" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>1229</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>238</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
@@ -6397,25 +6397,25 @@
     </row>
     <row r="18" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>1228</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>240</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>1230</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>242</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
@@ -6423,7 +6423,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>24</v>
@@ -6431,17 +6431,17 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -6481,7 +6481,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E2" s="6"/>
     </row>
@@ -6490,7 +6490,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="E3" s="6"/>
     </row>
@@ -6499,7 +6499,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="E4" s="6"/>
     </row>
@@ -6517,7 +6517,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="E6" s="6"/>
     </row>
@@ -6532,7 +6532,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>8</v>
@@ -6558,25 +6558,25 @@
     </row>
     <row r="9" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>300</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>1213</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>301</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>302</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -6584,25 +6584,25 @@
     </row>
     <row r="10" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>663</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>303</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>1213</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>665</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>305</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -6610,19 +6610,19 @@
     </row>
     <row r="11" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>58</v>
@@ -6636,25 +6636,25 @@
     </row>
     <row r="12" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>311</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>1213</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>313</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -6662,25 +6662,25 @@
     </row>
     <row r="13" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -6688,19 +6688,19 @@
     </row>
     <row r="14" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>58</v>
@@ -6714,25 +6714,25 @@
     </row>
     <row r="15" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>324</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>1214</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>326</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -6740,25 +6740,25 @@
     </row>
     <row r="16" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -6766,25 +6766,25 @@
     </row>
     <row r="17" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>1214</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>329</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>1216</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>331</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -6792,25 +6792,25 @@
     </row>
     <row r="18" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -6818,25 +6818,25 @@
     </row>
     <row r="19" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>333</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>1218</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>335</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -6844,25 +6844,25 @@
     </row>
     <row r="20" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -6870,25 +6870,25 @@
     </row>
     <row r="21" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -6896,7 +6896,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>24</v>
@@ -6909,7 +6909,7 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="10" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
@@ -6918,7 +6918,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
@@ -6928,7 +6928,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
@@ -7085,7 +7085,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -7093,7 +7093,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -7101,7 +7101,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -7117,7 +7117,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -7128,7 +7128,7 @@
         <v>42</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>8</v>
@@ -7154,25 +7154,25 @@
     </row>
     <row r="9" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="E9" s="5" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>1234</v>
-      </c>
-      <c r="D9" s="4" t="s">
+      <c r="G9" s="4" t="s">
         <v>356</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>1213</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>358</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
@@ -7180,25 +7180,25 @@
     </row>
     <row r="10" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>1232</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="E10" s="5" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>1234</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>1213</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>362</v>
-      </c>
       <c r="G10" s="4" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
@@ -7206,25 +7206,25 @@
     </row>
     <row r="11" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="E11" s="5" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F11" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D11" s="4" t="s">
+      <c r="G11" s="4" t="s">
         <v>365</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>1213</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>367</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
@@ -7232,25 +7232,25 @@
     </row>
     <row r="12" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="E12" s="5" t="s">
+        <v>1211</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>370</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>1213</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>372</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -7258,25 +7258,25 @@
     </row>
     <row r="13" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="E13" s="5" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>375</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>1214</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>377</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
@@ -7284,25 +7284,25 @@
     </row>
     <row r="14" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>45</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -7310,25 +7310,25 @@
     </row>
     <row r="15" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="E15" s="5" t="s">
+        <v>1212</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>1214</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>385</v>
-      </c>
       <c r="G15" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
@@ -7336,7 +7336,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>24</v>
@@ -7344,17 +7344,17 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="10" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -7392,7 +7392,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -7400,7 +7400,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -7408,7 +7408,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -7424,7 +7424,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -7435,7 +7435,7 @@
         <v>42</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>8</v>
@@ -7461,554 +7461,554 @@
     </row>
     <row r="9" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>390</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="E10" s="5" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>391</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>392</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>1193</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>394</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="E11" s="5" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>395</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>396</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>1194</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>398</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="E12" s="5" t="s">
+        <v>1193</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="C12" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>400</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>1195</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="E13" s="5" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>404</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>405</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>1196</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>406</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D14" s="4" t="s">
         <v>408</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="E14" s="5" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D14" s="4" t="s">
+      <c r="G14" s="4" t="s">
         <v>410</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>1197</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>411</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="E15" s="5" t="s">
+        <v>1196</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>414</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D15" s="4" t="s">
+      <c r="G15" s="4" t="s">
         <v>415</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>1198</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D16" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>419</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>420</v>
-      </c>
       <c r="E16" s="5" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>422</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="E17" s="5" t="s">
+        <v>1198</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>424</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>1200</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>425</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="E18" s="5" t="s">
+        <v>1199</v>
+      </c>
+      <c r="F18" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D18" s="4" t="s">
+      <c r="G18" s="4" t="s">
         <v>429</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>1201</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C19" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="E20" s="5" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>438</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>1203</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D21" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="E21" s="5" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G21" s="4" t="s">
         <v>442</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>443</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>1203</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D22" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="E22" s="5" t="s">
+        <v>1202</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>446</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>1204</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>1203</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>449</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>1258</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>1205</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>454</v>
-      </c>
       <c r="E24" s="5" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="E25" s="5" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>456</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>457</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>1106</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D26" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="E26" s="5" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G26" s="4" t="s">
         <v>460</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>461</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>1207</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D27" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="E27" s="5" t="s">
+        <v>1206</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="G27" s="4" t="s">
         <v>464</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>1208</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>467</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>1209</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D30" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="E30" s="5" t="s">
+        <v>1208</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D30" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>476</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>1210</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="E31" s="5" t="s">
+        <v>1209</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>480</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>1211</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="E32" s="5" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="G32" s="4" t="s">
         <v>484</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>485</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>1212</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
@@ -8016,7 +8016,7 @@
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>24</v>
@@ -8024,17 +8024,17 @@
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -8073,7 +8073,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -8081,7 +8081,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -8089,7 +8089,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -8105,7 +8105,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -8116,7 +8116,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>8</v>
@@ -8142,1801 +8142,1801 @@
     </row>
     <row r="9" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>747</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>748</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>749</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>1099</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>685</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>751</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>752</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>1099</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>753</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>757</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>758</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>759</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>1101</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>765</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="B13" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>761</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D13" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>762</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>1102</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>763</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>764</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>766</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>767</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>1103</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>769</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>770</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>1104</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B16" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>772</v>
       </c>
-      <c r="C16" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D16" s="4" t="s">
+      <c r="G16" s="4" t="s">
         <v>773</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>1105</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>774</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>775</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="B17" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>1151</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>776</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>777</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>1153</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="B18" s="4" t="s">
+        <v>777</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>1229</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>779</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>780</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>1154</v>
-      </c>
-      <c r="F18" s="4" t="s">
-        <v>1231</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>782</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>783</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>1154</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>753</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="B21" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>787</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>788</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D21" s="4" t="s">
+      <c r="G21" s="4" t="s">
         <v>789</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>1156</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>790</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>1155</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>792</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D22" s="4" t="s">
+      <c r="G22" s="4" t="s">
         <v>793</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>1157</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>794</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>795</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>1157</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>799</v>
       </c>
-      <c r="C24" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D24" s="4" t="s">
+      <c r="G24" s="4" t="s">
         <v>800</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>1159</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>801</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="B25" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>803</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D25" s="4" t="s">
+      <c r="G25" s="4" t="s">
         <v>804</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>1160</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>805</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G26" s="4" t="s">
         <v>807</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>808</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>1161</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>809</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>808</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>809</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>1160</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>810</v>
       </c>
-      <c r="C27" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D27" s="4" t="s">
+      <c r="G27" s="4" t="s">
         <v>811</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>1162</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>812</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>813</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F28" s="4" t="s">
         <v>814</v>
       </c>
-      <c r="C28" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D28" s="4" t="s">
+      <c r="G28" s="4" t="s">
         <v>815</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>1163</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>816</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>817</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D29" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="G29" s="4" t="s">
         <v>900</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>1158</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>901</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>902</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B30" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>903</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D30" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>904</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>1164</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>905</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>906</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>906</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>907</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D31" s="4" t="s">
+      <c r="G31" s="4" t="s">
         <v>908</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>1164</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>909</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>910</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B32" s="4" t="s">
+        <v>909</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>910</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>911</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D32" s="4" t="s">
+      <c r="G32" s="4" t="s">
         <v>912</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>1165</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>913</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B33" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F33" s="4" t="s">
         <v>915</v>
       </c>
-      <c r="C33" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D33" s="4" t="s">
+      <c r="G33" s="4" t="s">
         <v>916</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>1166</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>917</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B34" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>918</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>919</v>
       </c>
-      <c r="C34" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D34" s="4" t="s">
+      <c r="G34" s="4" t="s">
         <v>920</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>1158</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>921</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>922</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F35" s="4" t="s">
         <v>923</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D35" s="4" t="s">
+      <c r="G35" s="4" t="s">
         <v>924</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>1167</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>925</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>926</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D36" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>927</v>
+      </c>
+      <c r="G36" s="4" t="s">
         <v>928</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>1158</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>929</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>930</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B37" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>931</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D37" s="4" t="s">
+      <c r="G37" s="4" t="s">
         <v>932</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>1168</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>933</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>934</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B39" s="4" t="s">
+        <v>936</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>1230</v>
+      </c>
+      <c r="G39" s="4" t="s">
         <v>938</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>939</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>1168</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>1232</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>940</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>1250</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>941</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>942</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>1168</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>1252</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>943</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>942</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>943</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F41" s="4" t="s">
         <v>944</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D41" s="4" t="s">
+      <c r="G41" s="4" t="s">
         <v>945</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>1170</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>946</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>947</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>948</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D42" s="4" t="s">
+      <c r="G42" s="4" t="s">
         <v>949</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>1167</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>950</v>
-      </c>
-      <c r="G42" s="4" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D43" s="4" t="s">
+        <v>951</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="G43" s="4" t="s">
         <v>953</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>1158</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>954</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>956</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D44" s="4" t="s">
+      <c r="G44" s="4" t="s">
         <v>957</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>1168</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>958</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>959</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>959</v>
+      </c>
+      <c r="E45" s="5" t="s">
+        <v>1169</v>
+      </c>
+      <c r="F45" s="4" t="s">
         <v>960</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D45" s="4" t="s">
+      <c r="G45" s="4" t="s">
         <v>961</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>1171</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>962</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>963</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="B46" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>963</v>
+      </c>
+      <c r="E46" s="5" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>1231</v>
+      </c>
+      <c r="G46" s="4" t="s">
         <v>964</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>965</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>1168</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>1233</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="B48" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>969</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F48" s="4" t="s">
         <v>970</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D48" s="4" t="s">
+      <c r="G48" s="4" t="s">
         <v>971</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>1173</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>972</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>973</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="B49" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="E49" s="5" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F49" s="4" t="s">
         <v>974</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D49" s="4" t="s">
+      <c r="G49" s="4" t="s">
         <v>975</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>1098</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>976</v>
-      </c>
-      <c r="G49" s="4" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="B51" s="4" t="s">
+        <v>979</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F51" s="4" t="s">
         <v>981</v>
       </c>
-      <c r="C51" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D51" s="4" t="s">
+      <c r="G51" s="4" t="s">
         <v>982</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>1168</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>983</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="B52" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>984</v>
+      </c>
+      <c r="E52" s="5" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F52" s="4" t="s">
         <v>985</v>
       </c>
-      <c r="C52" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D52" s="4" t="s">
+      <c r="G52" s="4" t="s">
         <v>986</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>1168</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>987</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="B53" s="4" t="s">
+        <v>987</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>988</v>
+      </c>
+      <c r="E53" s="5" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>1249</v>
+      </c>
+      <c r="G53" s="4" t="s">
         <v>989</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>990</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>1168</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>1251</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>991</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="B54" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>991</v>
+      </c>
+      <c r="E54" s="5" t="s">
+        <v>1172</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>1248</v>
+      </c>
+      <c r="G54" s="4" t="s">
         <v>992</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>993</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>1174</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>1250</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>994</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="F55" s="4">
         <v>150</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B56" s="4" t="s">
+        <v>996</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="E56" s="5" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F56" s="4" t="s">
         <v>998</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D56" s="4" t="s">
+      <c r="G56" s="4" t="s">
         <v>999</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>1167</v>
-      </c>
-      <c r="F56" s="4" t="s">
-        <v>1000</v>
-      </c>
-      <c r="G56" s="4" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="F57" s="4">
         <v>4.2</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="B58" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>1004</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>1005</v>
       </c>
-      <c r="C58" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D58" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>1006</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>1168</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>1007</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="B59" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F59" s="4" t="s">
         <v>1009</v>
       </c>
-      <c r="C59" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D59" s="4" t="s">
+      <c r="G59" s="4" t="s">
         <v>1010</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>1168</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>1011</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="B60" s="4" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F60" s="4" t="s">
         <v>1013</v>
       </c>
-      <c r="C60" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D60" s="4" t="s">
+      <c r="G60" s="4" t="s">
         <v>1014</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>1168</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>1015</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
       <c r="B61" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>1166</v>
+      </c>
+      <c r="F61" s="4" t="s">
         <v>1017</v>
       </c>
-      <c r="C61" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D61" s="4" t="s">
+      <c r="G61" s="4" t="s">
         <v>1018</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>1168</v>
-      </c>
-      <c r="F61" s="4" t="s">
-        <v>1019</v>
-      </c>
-      <c r="G61" s="4" t="s">
-        <v>1020</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
       <c r="B62" s="4" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>1021</v>
       </c>
-      <c r="C62" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D62" s="4" t="s">
+      <c r="G62" s="4" t="s">
         <v>1022</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>1176</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>1023</v>
-      </c>
-      <c r="G62" s="4" t="s">
-        <v>1024</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="B63" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>1024</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>1025</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D63" s="4" t="s">
+      <c r="G63" s="4" t="s">
         <v>1026</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>1167</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>1027</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
       <c r="B64" s="4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G64" s="4" t="s">
         <v>1029</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>1030</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>1158</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="G64" s="4" t="s">
-        <v>1031</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="B65" s="4" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F65" s="4" t="s">
         <v>1032</v>
       </c>
-      <c r="C65" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D65" s="4" t="s">
+      <c r="G65" s="4" t="s">
         <v>1033</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>1158</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>1034</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="B66" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="G66" s="4" t="s">
         <v>1036</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>1037</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>1177</v>
-      </c>
-      <c r="F66" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="G66" s="4" t="s">
-        <v>1038</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="B67" s="4" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="G67" s="4" t="s">
         <v>1039</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>1040</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>1177</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="B68" s="4" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>1176</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="G68" s="4" t="s">
         <v>1042</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>1043</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>1178</v>
-      </c>
-      <c r="F68" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="G68" s="4" t="s">
-        <v>1044</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="B69" s="4" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F69" s="4" t="s">
         <v>1045</v>
       </c>
-      <c r="C69" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D69" s="4" t="s">
+      <c r="G69" s="4" t="s">
         <v>1046</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>1179</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>1047</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>1048</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="4" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="B70" s="4" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>1178</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="G70" s="4" t="s">
         <v>1049</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>1050</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>1180</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>1051</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="4" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="B71" s="4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>1179</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="G71" s="4" t="s">
         <v>1052</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>1053</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>1181</v>
-      </c>
-      <c r="F71" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="G71" s="4" t="s">
-        <v>1054</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="4" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
       <c r="B72" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="E72" s="5" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F72" s="4" t="s">
         <v>818</v>
       </c>
-      <c r="C72" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D72" s="4" t="s">
+      <c r="G72" s="4" t="s">
         <v>819</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>1182</v>
-      </c>
-      <c r="F72" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>821</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="4" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="B73" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="E73" s="5" t="s">
+        <v>1181</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="G73" s="4" t="s">
         <v>822</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>823</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>1183</v>
-      </c>
-      <c r="F73" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="G73" s="4" t="s">
-        <v>824</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="4" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="B74" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="E74" s="5" t="s">
+        <v>1182</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="G74" s="4" t="s">
         <v>825</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D74" s="4" t="s">
-        <v>826</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>1184</v>
-      </c>
-      <c r="F74" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="G74" s="4" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="4" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="B75" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>827</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="G75" s="4" t="s">
         <v>828</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>829</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>1185</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="4" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="B76" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="G76" s="4" t="s">
         <v>831</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>832</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>1186</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="77" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="4" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="B77" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="E77" s="5" t="s">
+        <v>1185</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="G77" s="4" t="s">
         <v>834</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>835</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>1187</v>
-      </c>
-      <c r="F77" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="G77" s="4" t="s">
-        <v>836</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="4" t="s">
-        <v>1089</v>
+        <v>1087</v>
       </c>
       <c r="B78" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>836</v>
+      </c>
+      <c r="E78" s="5" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="G78" s="4" t="s">
         <v>837</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>838</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>1188</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="G78" s="4" t="s">
-        <v>839</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="4" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="B79" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="E79" s="5" t="s">
+        <v>1187</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="G79" s="4" t="s">
         <v>840</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>841</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>1189</v>
-      </c>
-      <c r="F79" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="G79" s="4" t="s">
-        <v>842</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="4" t="s">
-        <v>1091</v>
+        <v>1089</v>
       </c>
       <c r="B80" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>1188</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="G80" s="4" t="s">
         <v>843</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>844</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>1190</v>
-      </c>
-      <c r="F80" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="G80" s="4" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="4" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="B81" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>1188</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="G81" s="4" t="s">
         <v>846</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>847</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>1190</v>
-      </c>
-      <c r="F81" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="G81" s="4" t="s">
-        <v>848</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="4" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="B82" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>1188</v>
+      </c>
+      <c r="F82" s="4" t="s">
         <v>849</v>
       </c>
-      <c r="C82" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D82" s="4" t="s">
+      <c r="G82" s="4" t="s">
         <v>850</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>1190</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>851</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>852</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="4" t="s">
-        <v>1094</v>
+        <v>1092</v>
       </c>
       <c r="B83" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>1188</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="G83" s="4" t="s">
         <v>853</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D83" s="4" t="s">
-        <v>854</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>1190</v>
-      </c>
-      <c r="F83" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="G83" s="4" t="s">
-        <v>855</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="4" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="B84" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="E84" s="5" t="s">
+        <v>1188</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="G84" s="4" t="s">
         <v>856</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D84" s="4" t="s">
-        <v>857</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>1190</v>
-      </c>
-      <c r="F84" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="G84" s="4" t="s">
-        <v>858</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="4" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="4" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="B86" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="E86" s="5" t="s">
+        <v>1190</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G86" s="4" t="s">
         <v>861</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D86" s="4" t="s">
-        <v>862</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>1192</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="G86" s="4" t="s">
-        <v>863</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>24</v>
@@ -9944,17 +9944,17 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" s="10" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -9994,7 +9994,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -10002,7 +10002,7 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -10010,7 +10010,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -10026,7 +10026,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -10037,7 +10037,7 @@
         <v>7</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>8</v>
@@ -10063,111 +10063,111 @@
     </row>
     <row r="9" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>19</v>
+        <v>1252</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>23</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>25</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="150" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="F10" s="20" t="s">
         <v>30</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>36</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>37</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>58</v>
@@ -10178,65 +10178,65 @@
     </row>
     <row r="14" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>49</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>57</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>58</v>
@@ -10247,111 +10247,111 @@
     </row>
     <row r="17" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>61</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="F18" s="4">
         <v>9876543909</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>78</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>81</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>84</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>58</v>
@@ -10362,19 +10362,19 @@
     </row>
     <row r="22" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>1113</v>
+        <v>1111</v>
       </c>
       <c r="F22" s="4">
         <v>9876543210</v>
@@ -10385,68 +10385,68 @@
     </row>
     <row r="23" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="F23" s="4">
         <v>123456</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="F24" s="4">
         <v>654321</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>95</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="G25" s="4" t="s">
         <v>96</v>
@@ -10454,22 +10454,22 @@
     </row>
     <row r="26" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>537</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>538</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>1117</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>539</v>
       </c>
       <c r="G26" s="4" t="s">
         <v>100</v>
@@ -10477,19 +10477,19 @@
     </row>
     <row r="27" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>102</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>58</v>
@@ -10500,640 +10500,640 @@
     </row>
     <row r="28" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B28" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="G28" s="4" t="s">
         <v>541</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>1119</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B30" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="C30" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D30" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>547</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>1121</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F31" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D31" s="4" t="s">
+      <c r="G31" s="4" t="s">
         <v>551</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>1121</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>552</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B32" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>1120</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="G32" s="4" t="s">
         <v>554</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>555</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>1122</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>673</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B33" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>557</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>558</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>1123</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>675</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B34" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="G34" s="4" t="s">
         <v>560</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>561</v>
-      </c>
-      <c r="E34" s="8" t="s">
-        <v>1124</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>674</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>563</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>564</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>1125</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>676</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="G36" s="4" t="s">
         <v>566</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>567</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>1125</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>677</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B37" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>568</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>569</v>
       </c>
-      <c r="C37" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D37" s="4" t="s">
+      <c r="G37" s="4" t="s">
         <v>570</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>1125</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>1111</v>
+        <v>1109</v>
       </c>
       <c r="F38" s="4">
         <v>9876543210</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B39" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="G39" s="4" t="s">
         <v>576</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>577</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>1111</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>678</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>58</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="G41" s="4" t="s">
         <v>582</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="E41" s="8" t="s">
-        <v>1127</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>584</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="4" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F42" s="4" t="s">
         <v>585</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>586</v>
-      </c>
-      <c r="E42" s="8" t="s">
-        <v>1128</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>587</v>
-      </c>
       <c r="G42" s="4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>588</v>
       </c>
-      <c r="C43" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D43" s="4" t="s">
+      <c r="G43" s="4" t="s">
         <v>589</v>
-      </c>
-      <c r="E43" s="8" t="s">
-        <v>1129</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>590</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>591</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>747</v>
-      </c>
-      <c r="D44" s="4" t="s">
+      <c r="G44" s="4" t="s">
         <v>593</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>1130</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>1129</v>
+      </c>
+      <c r="F45" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D45" s="4" t="s">
+      <c r="G45" s="4" t="s">
         <v>597</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>1131</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>598</v>
-      </c>
-      <c r="G45" s="4" t="s">
-        <v>599</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B46" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>1130</v>
+      </c>
+      <c r="F46" s="4" t="s">
         <v>600</v>
       </c>
-      <c r="C46" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>601</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>1132</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>602</v>
-      </c>
       <c r="G46" s="4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="4" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F47" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="C47" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>1133</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>605</v>
-      </c>
       <c r="G47" s="4" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B48" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>1132</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="G48" s="4" t="s">
         <v>606</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>607</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>1134</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>608</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="4" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="B51" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="G51" s="4" t="s">
         <v>613</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>614</v>
-      </c>
-      <c r="E51" s="8" t="s">
-        <v>1137</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B52" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>1136</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="G52" s="4" t="s">
         <v>616</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>617</v>
-      </c>
-      <c r="E52" s="8" t="s">
-        <v>1138</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>680</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="B53" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="G53" s="4" t="s">
         <v>619</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="E53" s="8" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>497</v>
-      </c>
-      <c r="G53" s="4" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="4" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>58</v>
@@ -11144,134 +11144,134 @@
     </row>
     <row r="56" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B57" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>627</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>1139</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="G57" s="4" t="s">
         <v>628</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>629</v>
-      </c>
-      <c r="E57" s="8" t="s">
-        <v>1141</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>681</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B58" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="C58" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D58" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>632</v>
-      </c>
-      <c r="E58" s="8" t="s">
-        <v>1142</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>633</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="4" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="B59" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="G59" s="4" t="s">
         <v>635</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>636</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>1143</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>682</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="4" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B60" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>637</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="G60" s="4" t="s">
         <v>638</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>639</v>
-      </c>
-      <c r="E60" s="8" t="s">
-        <v>1143</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>683</v>
-      </c>
-      <c r="G60" s="4" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="4" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>58</v>
@@ -11282,65 +11282,65 @@
     </row>
     <row r="62" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="4" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B62" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="C62" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>644</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>1145</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>645</v>
-      </c>
       <c r="G62" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="4" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B63" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>1144</v>
+      </c>
+      <c r="F63" s="4" t="s">
         <v>646</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D63" s="4" t="s">
+      <c r="G63" s="4" t="s">
         <v>647</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>1146</v>
-      </c>
-      <c r="F63" s="4" t="s">
-        <v>648</v>
-      </c>
-      <c r="G63" s="4" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="4" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>58</v>
@@ -11351,122 +11351,122 @@
     </row>
     <row r="65" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="4" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="B65" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="E65" s="8" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="G65" s="4" t="s">
         <v>652</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="E65" s="8" t="s">
-        <v>1147</v>
-      </c>
-      <c r="F65" s="4" t="s">
-        <v>684</v>
-      </c>
-      <c r="G65" s="4" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="4" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="4" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B67" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="E67" s="8" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="G67" s="4" t="s">
         <v>657</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>658</v>
-      </c>
-      <c r="E67" s="8" t="s">
-        <v>1148</v>
-      </c>
-      <c r="F67" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="G67" s="4" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="4" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="4" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B69" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>1252</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="E69" s="8" t="s">
+        <v>1148</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="G69" s="4" t="s">
         <v>662</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>1254</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>663</v>
-      </c>
-      <c r="E69" s="8" t="s">
-        <v>1150</v>
-      </c>
-      <c r="F69" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="G69" s="4" t="s">
-        <v>664</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="10" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>24</v>
@@ -11479,7 +11479,7 @@
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="10" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C72" s="4"/>
       <c r="D72" s="4"/>
@@ -11489,7 +11489,7 @@
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C73" s="4"/>
       <c r="D73" s="4"/>
@@ -11499,7 +11499,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C74" s="4"/>
       <c r="D74" s="4"/>
